--- a/artfynd/A 11819-2024 artfynd.xlsx
+++ b/artfynd/A 11819-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,72 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16362331</v>
+        <v>107490711</v>
       </c>
       <c r="B2" t="n">
-        <v>44319</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102366</v>
+        <v>2667</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ängsmetallvinge</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Adscita statices</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åkeholm 0750/4350, Bl</t>
+          <t>Jätteask i Boarp, Bl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484219.5627458554</v>
+        <v>484330</v>
       </c>
       <c r="R2" t="n">
-        <v>6238409.414184112</v>
+        <v>6238217</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-07-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2017-12-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-07-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På Knautia</t>
+          <t>2017-12-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,19 +756,482 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Gammal ask (GAMASK)</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Anders Engström</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Via Anders Engström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>107490710</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79707</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6431</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bacidia rubella</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Jätteask i Boarp, Bl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>484330</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6238217</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Karlshamn</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Asarum</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2017-12-13</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2017-12-13</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Gammal ask (GAMASK)</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anders Engström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Via Anders Engström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>107490712</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Jätteask i Boarp, Bl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>484330</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6238217</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlshamn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Asarum</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2017-12-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2017-12-13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Gammal ask (GAMASK)</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anders Engström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Anders Engström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>16362331</v>
+      </c>
+      <c r="B5" t="n">
+        <v>45033</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102366</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ängsmetallvinge</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Adscita statices</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Åkeholm 0750/4350, Bl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>484220</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6238409</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlshamn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Asarum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2014-07-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2014-07-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På Knautia</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Gunnar Hallin</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Gunnar Hallin</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>93742337</v>
+      </c>
+      <c r="B6" t="n">
+        <v>111128</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Småvänderot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Valeriana dioica</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Boarp N, Bl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>484356</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6238193</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Karlshamn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Asarum</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>K-Khn-0407</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>1980-01-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1989-12-31</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Åke Widgren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Göran Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11819-2024 artfynd.xlsx
+++ b/artfynd/A 11819-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107490711</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107490710</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107490712</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16362331</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,8 +1257,20 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93742337</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>